--- a/artfynd/A 38452-2023 artfynd.xlsx
+++ b/artfynd/A 38452-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38452-2023 artfynd.xlsx
+++ b/artfynd/A 38452-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83508683</v>
+        <v>97356916</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1469</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sutarp1:4, Sm</t>
+          <t>Norr om Sutap, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479089.2691443865</v>
+        <v>479123</v>
       </c>
       <c r="R2" t="n">
-        <v>6438913.860167113</v>
+        <v>6439012</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +738,19 @@
           <t>Adelöv</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>B7760D91-E728-473B-AFF5-41E6AC02EDA9</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I nyckelbiotop</t>
+          <t>NVI inventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,53 +765,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Lennart Sundh</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Gustav Enander</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97356849</v>
+        <v>97356846</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479066.7396648183</v>
+        <v>479130</v>
       </c>
       <c r="R3" t="n">
-        <v>6438960.499702281</v>
+        <v>6439036</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +845,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,53 +879,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97356845</v>
+        <v>83508683</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Sutarp, Sm</t>
+          <t>Sutarp1:4, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479184.413496924</v>
+        <v>479089</v>
       </c>
       <c r="R4" t="n">
-        <v>6438978.384963923</v>
+        <v>6438914</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,29 +946,24 @@
           <t>Adelöv</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>B7760D91-E728-473B-AFF5-41E6AC02EDA9</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>NVI inventering</t>
+          <t>I nyckelbiotop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,49 +978,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lennart Sundh</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Marielle Gustafsson, Gustav Enander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97356846</v>
+        <v>97356849</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479129.6292759712</v>
+        <v>479066</v>
       </c>
       <c r="R5" t="n">
-        <v>6439035.236327431</v>
+        <v>6438961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,19 +1062,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1156,53 +1096,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97356916</v>
+        <v>97356844</v>
       </c>
       <c r="B6" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1469</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr om Sutap, Sm</t>
+          <t>Norr om Sutarp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479123.1546236594</v>
+        <v>479221</v>
       </c>
       <c r="R6" t="n">
-        <v>6439012.538895437</v>
+        <v>6438943</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,19 +1164,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1270,6 +1195,210 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97356845</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr om Sutarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>479184</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6438978</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Adelöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>NVI inventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97356850</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr om Sutarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>479051</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6438936</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Adelöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>NVI inventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38452-2023 artfynd.xlsx
+++ b/artfynd/A 38452-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356846</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83508683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356845</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,8 +1434,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>